--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120029553</v>
+        <v>120029292</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522558</v>
+        <v>522544</v>
       </c>
       <c r="R2" t="n">
-        <v>6717836</v>
+        <v>6717800</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -918,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120029292</v>
+        <v>120030239</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,31 +931,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522544</v>
+        <v>522507</v>
       </c>
       <c r="R4" t="n">
-        <v>6717800</v>
+        <v>6717797</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120030239</v>
+        <v>120029553</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1052,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522507</v>
+        <v>522558</v>
       </c>
       <c r="R5" t="n">
-        <v>6717797</v>
+        <v>6717836</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062971</v>
+        <v>120063976</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,32 +1177,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522583</v>
+        <v>522496</v>
       </c>
       <c r="R6" t="n">
-        <v>6717826</v>
+        <v>6717834</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 10st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063976</v>
+        <v>120062971</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,31 +1303,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522496</v>
+        <v>522583</v>
       </c>
       <c r="R7" t="n">
-        <v>6717834</v>
+        <v>6717826</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10st</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120029292</v>
+        <v>120029553</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522544</v>
+        <v>522558</v>
       </c>
       <c r="R2" t="n">
-        <v>6717800</v>
+        <v>6717836</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030156</v>
+        <v>120030239</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522499</v>
+        <v>522507</v>
       </c>
       <c r="R3" t="n">
-        <v>6717785</v>
+        <v>6717797</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en tallåga</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120030239</v>
+        <v>120030156</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,35 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -968,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522507</v>
+        <v>522499</v>
       </c>
       <c r="R4" t="n">
-        <v>6717797</v>
+        <v>6717785</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1007,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en tallåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120029553</v>
+        <v>120029292</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,31 +1055,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522558</v>
+        <v>522544</v>
       </c>
       <c r="R5" t="n">
-        <v>6717836</v>
+        <v>6717800</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1124,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063976</v>
+        <v>120062971</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,31 +1177,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1210,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522496</v>
+        <v>522583</v>
       </c>
       <c r="R6" t="n">
-        <v>6717834</v>
+        <v>6717826</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1256,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 10st</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120062971</v>
+        <v>120063976</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,32 +1304,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522583</v>
+        <v>522496</v>
       </c>
       <c r="R7" t="n">
-        <v>6717826</v>
+        <v>6717834</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 10st</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120029553</v>
+        <v>120029292</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522558</v>
+        <v>522544</v>
       </c>
       <c r="R2" t="n">
-        <v>6717836</v>
+        <v>6717800</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1039,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120029292</v>
+        <v>120029553</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,27 +1056,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522544</v>
+        <v>522558</v>
       </c>
       <c r="R5" t="n">
-        <v>6717800</v>
+        <v>6717836</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120029292</v>
+        <v>120030239</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522544</v>
+        <v>522507</v>
       </c>
       <c r="R2" t="n">
-        <v>6717800</v>
+        <v>6717797</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030239</v>
+        <v>120030156</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522507</v>
+        <v>522499</v>
       </c>
       <c r="R3" t="n">
-        <v>6717797</v>
+        <v>6717785</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120030156</v>
+        <v>120029292</v>
       </c>
       <c r="B4" t="n">
         <v>8432</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522499</v>
+        <v>522544</v>
       </c>
       <c r="R4" t="n">
-        <v>6717785</v>
+        <v>6717800</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en tallåga</t>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,7 +1043,7 @@
         <v>120029553</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>120062971</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>120063976</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030239</v>
+        <v>120029292</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522507</v>
+        <v>522544</v>
       </c>
       <c r="R2" t="n">
-        <v>6717797</v>
+        <v>6717800</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030156</v>
+        <v>120029553</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,27 +813,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522499</v>
+        <v>522558</v>
       </c>
       <c r="R3" t="n">
-        <v>6717785</v>
+        <v>6717836</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en tallåga</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120029292</v>
+        <v>120030156</v>
       </c>
       <c r="B4" t="n">
         <v>8432</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522544</v>
+        <v>522499</v>
       </c>
       <c r="R4" t="n">
-        <v>6717800</v>
+        <v>6717785</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>På en tallåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120029553</v>
+        <v>120030239</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1052,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522558</v>
+        <v>522507</v>
       </c>
       <c r="R5" t="n">
-        <v>6717836</v>
+        <v>6717797</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062971</v>
+        <v>120063976</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,32 +1177,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522583</v>
+        <v>522496</v>
       </c>
       <c r="R6" t="n">
-        <v>6717826</v>
+        <v>6717834</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 10st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063976</v>
+        <v>120062971</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,31 +1303,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522496</v>
+        <v>522583</v>
       </c>
       <c r="R7" t="n">
-        <v>6717834</v>
+        <v>6717826</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10st</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120029292</v>
+        <v>120030239</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522544</v>
+        <v>522507</v>
       </c>
       <c r="R2" t="n">
-        <v>6717800</v>
+        <v>6717797</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120029553</v>
+        <v>120029292</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +812,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522558</v>
+        <v>522544</v>
       </c>
       <c r="R3" t="n">
-        <v>6717836</v>
+        <v>6717800</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120030239</v>
+        <v>120029553</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1052,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522507</v>
+        <v>522558</v>
       </c>
       <c r="R5" t="n">
-        <v>6717797</v>
+        <v>6717836</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120029292</v>
+        <v>120029553</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,27 +812,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522544</v>
+        <v>522558</v>
       </c>
       <c r="R3" t="n">
-        <v>6717800</v>
+        <v>6717836</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120030156</v>
+        <v>120029292</v>
       </c>
       <c r="B4" t="n">
         <v>8432</v>
@@ -963,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522499</v>
+        <v>522544</v>
       </c>
       <c r="R4" t="n">
-        <v>6717785</v>
+        <v>6717800</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -998,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1007,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en tallåga</t>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120029553</v>
+        <v>120030156</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,31 +1055,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522558</v>
+        <v>522499</v>
       </c>
       <c r="R5" t="n">
-        <v>6717836</v>
+        <v>6717785</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1124,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063976</v>
+        <v>120062971</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,31 +1177,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1210,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522496</v>
+        <v>522583</v>
       </c>
       <c r="R6" t="n">
-        <v>6717834</v>
+        <v>6717826</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1256,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 10st</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120062971</v>
+        <v>120063976</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,32 +1304,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522583</v>
+        <v>522496</v>
       </c>
       <c r="R7" t="n">
-        <v>6717826</v>
+        <v>6717834</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 10st</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030239</v>
+        <v>120030156</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522507</v>
+        <v>522499</v>
       </c>
       <c r="R2" t="n">
-        <v>6717797</v>
+        <v>6717785</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120029553</v>
+        <v>120030239</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +809,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522558</v>
+        <v>522507</v>
       </c>
       <c r="R3" t="n">
-        <v>6717836</v>
+        <v>6717797</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120029292</v>
+        <v>120029553</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,27 +934,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522544</v>
+        <v>522558</v>
       </c>
       <c r="R4" t="n">
-        <v>6717800</v>
+        <v>6717836</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -997,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,12 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120030156</v>
+        <v>120029292</v>
       </c>
       <c r="B5" t="n">
         <v>8432</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522499</v>
+        <v>522544</v>
       </c>
       <c r="R5" t="n">
-        <v>6717785</v>
+        <v>6717800</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en tallåga</t>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030156</v>
+        <v>120030239</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522499</v>
+        <v>522507</v>
       </c>
       <c r="R2" t="n">
-        <v>6717785</v>
+        <v>6717797</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en tallåga</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120030239</v>
+        <v>120029292</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522507</v>
+        <v>522544</v>
       </c>
       <c r="R3" t="n">
-        <v>6717797</v>
+        <v>6717800</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120029292</v>
+        <v>120030156</v>
       </c>
       <c r="B5" t="n">
         <v>8432</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522544</v>
+        <v>522499</v>
       </c>
       <c r="R5" t="n">
-        <v>6717800</v>
+        <v>6717785</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>På en tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120030239</v>
+        <v>120029292</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522507</v>
+        <v>522544</v>
       </c>
       <c r="R2" t="n">
-        <v>6717797</v>
+        <v>6717800</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera lågor,tall och gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120029292</v>
+        <v>120030239</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +809,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522544</v>
+        <v>522507</v>
       </c>
       <c r="R3" t="n">
-        <v>6717800</v>
+        <v>6717797</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera lågor,tall och gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062971</v>
+        <v>120063976</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,32 +1177,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522583</v>
+        <v>522496</v>
       </c>
       <c r="R6" t="n">
-        <v>6717826</v>
+        <v>6717834</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 10st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063976</v>
+        <v>120062971</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,31 +1303,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522496</v>
+        <v>522583</v>
       </c>
       <c r="R7" t="n">
-        <v>6717834</v>
+        <v>6717826</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10st</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1653,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285145</v>
+        <v>121285105</v>
       </c>
       <c r="B10" t="n">
-        <v>91963</v>
+        <v>91969</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522497</v>
+        <v>522501</v>
       </c>
       <c r="R10" t="n">
-        <v>6717850</v>
+        <v>6717812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285106</v>
+        <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>56552</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522496</v>
+        <v>522497</v>
       </c>
       <c r="R11" t="n">
-        <v>6717794</v>
+        <v>6717850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285105</v>
+        <v>121285106</v>
       </c>
       <c r="B12" t="n">
-        <v>91959</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4363</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522501</v>
+        <v>522496</v>
       </c>
       <c r="R12" t="n">
-        <v>6717812</v>
+        <v>6717794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R14" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285188</v>
+        <v>121285110</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522528</v>
+        <v>522491</v>
       </c>
       <c r="R15" t="n">
-        <v>6717827</v>
+        <v>6717727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285145</v>
+        <v>121285106</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>56555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522497</v>
+        <v>522496</v>
       </c>
       <c r="R11" t="n">
-        <v>6717850</v>
+        <v>6717794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285106</v>
+        <v>121285145</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>91973</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522496</v>
+        <v>522497</v>
       </c>
       <c r="R12" t="n">
-        <v>6717794</v>
+        <v>6717850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285106</v>
+        <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>56555</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522496</v>
+        <v>522497</v>
       </c>
       <c r="R11" t="n">
-        <v>6717794</v>
+        <v>6717850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285145</v>
+        <v>121285106</v>
       </c>
       <c r="B12" t="n">
-        <v>91973</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522497</v>
+        <v>522496</v>
       </c>
       <c r="R12" t="n">
-        <v>6717850</v>
+        <v>6717794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1653,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285105</v>
+        <v>121285106</v>
       </c>
       <c r="B10" t="n">
-        <v>91969</v>
+        <v>56555</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,25 +1665,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522501</v>
+        <v>522496</v>
       </c>
       <c r="R10" t="n">
-        <v>6717812</v>
+        <v>6717794</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285145</v>
+        <v>121285105</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>91969</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522497</v>
+        <v>522501</v>
       </c>
       <c r="R11" t="n">
-        <v>6717850</v>
+        <v>6717812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285106</v>
+        <v>121285145</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>91973</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522496</v>
+        <v>522497</v>
       </c>
       <c r="R12" t="n">
-        <v>6717794</v>
+        <v>6717850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
+          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285188</v>
+        <v>121285110</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522528</v>
+        <v>522491</v>
       </c>
       <c r="R14" t="n">
-        <v>6717827</v>
+        <v>6717727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>8432</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R15" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
+          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285105</v>
+        <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>91969</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522501</v>
+        <v>522497</v>
       </c>
       <c r="R11" t="n">
-        <v>6717812</v>
+        <v>6717850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285145</v>
+        <v>121285105</v>
       </c>
       <c r="B12" t="n">
-        <v>91973</v>
+        <v>91981</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522497</v>
+        <v>522501</v>
       </c>
       <c r="R12" t="n">
-        <v>6717850</v>
+        <v>6717812</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1967,17 +1967,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285117</v>
+        <v>121285110</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>5189</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522497</v>
+        <v>522491</v>
       </c>
       <c r="R13" t="n">
-        <v>6717826</v>
+        <v>6717727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R14" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285188</v>
+        <v>121285117</v>
       </c>
       <c r="B15" t="n">
         <v>8432</v>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522528</v>
+        <v>522497</v>
       </c>
       <c r="R15" t="n">
-        <v>6717827</v>
+        <v>6717826</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1763,7 +1763,7 @@
         <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>121285105</v>
       </c>
       <c r="B12" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285110</v>
+        <v>121285117</v>
       </c>
       <c r="B13" t="n">
-        <v>5189</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522491</v>
+        <v>522497</v>
       </c>
       <c r="R13" t="n">
-        <v>6717727</v>
+        <v>6717826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
+          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285117</v>
+        <v>121285110</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522497</v>
+        <v>522491</v>
       </c>
       <c r="R15" t="n">
-        <v>6717826</v>
+        <v>6717727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>121285106</v>
       </c>
       <c r="B10" t="n">
-        <v>56555</v>
+        <v>56558</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285145</v>
+        <v>121285105</v>
       </c>
       <c r="B11" t="n">
-        <v>91986</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522497</v>
+        <v>522501</v>
       </c>
       <c r="R11" t="n">
-        <v>6717850</v>
+        <v>6717812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285105</v>
+        <v>121285145</v>
       </c>
       <c r="B12" t="n">
-        <v>91982</v>
+        <v>91989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522501</v>
+        <v>522497</v>
       </c>
       <c r="R12" t="n">
-        <v>6717812</v>
+        <v>6717850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285117</v>
+        <v>121285110</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>5192</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522497</v>
+        <v>522491</v>
       </c>
       <c r="R13" t="n">
-        <v>6717826</v>
+        <v>6717727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285188</v>
+        <v>121285117</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522528</v>
+        <v>522497</v>
       </c>
       <c r="R14" t="n">
-        <v>6717827</v>
+        <v>6717826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>8435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R15" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
+          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1653,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285106</v>
+        <v>121285105</v>
       </c>
       <c r="B10" t="n">
-        <v>56558</v>
+        <v>91985</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,25 +1665,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522496</v>
+        <v>522501</v>
       </c>
       <c r="R10" t="n">
-        <v>6717794</v>
+        <v>6717812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285105</v>
+        <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>91989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522501</v>
+        <v>522497</v>
       </c>
       <c r="R11" t="n">
-        <v>6717812</v>
+        <v>6717850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285145</v>
+        <v>121285106</v>
       </c>
       <c r="B12" t="n">
-        <v>91989</v>
+        <v>56558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522497</v>
+        <v>522496</v>
       </c>
       <c r="R12" t="n">
-        <v>6717850</v>
+        <v>6717794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B13" t="n">
-        <v>5192</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R13" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285117</v>
+        <v>121285110</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522497</v>
+        <v>522491</v>
       </c>
       <c r="R14" t="n">
-        <v>6717826</v>
+        <v>6717727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285188</v>
+        <v>121285117</v>
       </c>
       <c r="B15" t="n">
         <v>8435</v>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522528</v>
+        <v>522497</v>
       </c>
       <c r="R15" t="n">
-        <v>6717827</v>
+        <v>6717826</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>121285105</v>
       </c>
       <c r="B10" t="n">
-        <v>91985</v>
+        <v>91991</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285145</v>
+        <v>121285106</v>
       </c>
       <c r="B11" t="n">
-        <v>91989</v>
+        <v>56559</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522497</v>
+        <v>522496</v>
       </c>
       <c r="R11" t="n">
-        <v>6717850</v>
+        <v>6717794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285106</v>
+        <v>121285145</v>
       </c>
       <c r="B12" t="n">
-        <v>56558</v>
+        <v>91995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522496</v>
+        <v>522497</v>
       </c>
       <c r="R12" t="n">
-        <v>6717794</v>
+        <v>6717850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285106</v>
+        <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>56559</v>
+        <v>91995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522496</v>
+        <v>522497</v>
       </c>
       <c r="R11" t="n">
-        <v>6717794</v>
+        <v>6717850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285145</v>
+        <v>121285106</v>
       </c>
       <c r="B12" t="n">
-        <v>91995</v>
+        <v>56559</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522497</v>
+        <v>522496</v>
       </c>
       <c r="R12" t="n">
-        <v>6717850</v>
+        <v>6717794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1653,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285105</v>
+        <v>121285145</v>
       </c>
       <c r="B10" t="n">
-        <v>91991</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522501</v>
+        <v>522497</v>
       </c>
       <c r="R10" t="n">
-        <v>6717812</v>
+        <v>6717850</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285145</v>
+        <v>121285105</v>
       </c>
       <c r="B11" t="n">
-        <v>91995</v>
+        <v>91992</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522497</v>
+        <v>522501</v>
       </c>
       <c r="R11" t="n">
-        <v>6717850</v>
+        <v>6717812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
         <v>121285106</v>
       </c>
       <c r="B12" t="n">
-        <v>56559</v>
+        <v>56560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285188</v>
+        <v>121285117</v>
       </c>
       <c r="B13" t="n">
         <v>8435</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522528</v>
+        <v>522497</v>
       </c>
       <c r="R13" t="n">
-        <v>6717827</v>
+        <v>6717826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285117</v>
+        <v>121285188</v>
       </c>
       <c r="B15" t="n">
         <v>8435</v>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522497</v>
+        <v>522528</v>
       </c>
       <c r="R15" t="n">
-        <v>6717826</v>
+        <v>6717827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B14" t="n">
-        <v>5192</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R14" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285188</v>
+        <v>121285110</v>
       </c>
       <c r="B15" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522528</v>
+        <v>522491</v>
       </c>
       <c r="R15" t="n">
-        <v>6717827</v>
+        <v>6717727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1653,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285145</v>
+        <v>121285105</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>91992</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522497</v>
+        <v>522501</v>
       </c>
       <c r="R10" t="n">
-        <v>6717850</v>
+        <v>6717812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285105</v>
+        <v>121285145</v>
       </c>
       <c r="B11" t="n">
-        <v>91992</v>
+        <v>91996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522501</v>
+        <v>522497</v>
       </c>
       <c r="R11" t="n">
-        <v>6717812</v>
+        <v>6717850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285188</v>
+        <v>121285110</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522528</v>
+        <v>522491</v>
       </c>
       <c r="R14" t="n">
-        <v>6717827</v>
+        <v>6717727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B15" t="n">
-        <v>5192</v>
+        <v>8435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R15" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1653,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285105</v>
+        <v>121285145</v>
       </c>
       <c r="B10" t="n">
-        <v>91992</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522501</v>
+        <v>522497</v>
       </c>
       <c r="R10" t="n">
-        <v>6717812</v>
+        <v>6717850</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285145</v>
+        <v>121285106</v>
       </c>
       <c r="B11" t="n">
-        <v>91996</v>
+        <v>56560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522497</v>
+        <v>522496</v>
       </c>
       <c r="R11" t="n">
-        <v>6717850</v>
+        <v>6717794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285106</v>
+        <v>121285105</v>
       </c>
       <c r="B12" t="n">
-        <v>56560</v>
+        <v>91992</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>4363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522496</v>
+        <v>522501</v>
       </c>
       <c r="R12" t="n">
-        <v>6717794</v>
+        <v>6717812</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285117</v>
+        <v>121285110</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522497</v>
+        <v>522491</v>
       </c>
       <c r="R13" t="n">
-        <v>6717826</v>
+        <v>6717727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285110</v>
+        <v>121285188</v>
       </c>
       <c r="B14" t="n">
-        <v>5192</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522491</v>
+        <v>522528</v>
       </c>
       <c r="R14" t="n">
-        <v>6717727</v>
+        <v>6717827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
+          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285188</v>
+        <v>121285117</v>
       </c>
       <c r="B15" t="n">
         <v>8435</v>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522528</v>
+        <v>522497</v>
       </c>
       <c r="R15" t="n">
-        <v>6717827</v>
+        <v>6717826</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>121285145</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>92001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285106</v>
+        <v>121285105</v>
       </c>
       <c r="B11" t="n">
-        <v>56560</v>
+        <v>91997</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>4363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522496</v>
+        <v>522501</v>
       </c>
       <c r="R11" t="n">
-        <v>6717794</v>
+        <v>6717812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285105</v>
+        <v>121285106</v>
       </c>
       <c r="B12" t="n">
-        <v>91992</v>
+        <v>56561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4363</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522501</v>
+        <v>522496</v>
       </c>
       <c r="R12" t="n">
-        <v>6717812</v>
+        <v>6717794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
         <v>121285110</v>
       </c>
       <c r="B13" t="n">
-        <v>5192</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285188</v>
+        <v>121285117</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>8436</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522528</v>
+        <v>522497</v>
       </c>
       <c r="R14" t="n">
-        <v>6717827</v>
+        <v>6717826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ellen Payne, Per Karlsson Linderum, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Ellen Payne</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285117</v>
+        <v>121285188</v>
       </c>
       <c r="B15" t="n">
-        <v>8435</v>
+        <v>8436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522497</v>
+        <v>522528</v>
       </c>
       <c r="R15" t="n">
-        <v>6717826</v>
+        <v>6717827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 31359-2024 artfynd.xlsx
+++ b/artfynd/A 31359-2024 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>120062971</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
